--- a/data/260815_자금관리_REV03.xlsx
+++ b/data/260815_자금관리_REV03.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CM\Desktop\테스트\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C0ADA8-F94E-4DA4-B390-1DBBFDBA8155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7210C0E8-47FA-475C-88D7-77E64CB9D129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="상세내역" sheetId="3" r:id="rId1"/>
@@ -570,11 +570,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -878,13 +878,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
       <c r="G1" s="28"/>
       <c r="I1" s="3" t="s">
         <v>61</v>
@@ -903,11 +903,11 @@
       </c>
     </row>
     <row r="2" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
       <c r="G2" s="28"/>
       <c r="I2" s="26">
         <f>SUMIF(H4:H45,"계약금",G4:G45)</f>
@@ -919,7 +919,7 @@
       </c>
       <c r="K2" s="26">
         <f>SUM(K4:K45)</f>
-        <v>2736370000</v>
+        <v>2680570000</v>
       </c>
       <c r="L2" s="26">
         <f>SUM(L4:L45)</f>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="J27" s="22"/>
       <c r="K27" s="7">
-        <v>62000000</v>
+        <v>6200000</v>
       </c>
       <c r="L27" s="7"/>
       <c r="M27" s="9"/>
@@ -1796,7 +1796,7 @@
       <c r="J29" s="22"/>
       <c r="K29" s="7"/>
       <c r="L29" s="7">
-        <f t="shared" ref="L28:L29" si="2">I29</f>
+        <f t="shared" ref="L29" si="2">I29</f>
         <v>6200000</v>
       </c>
       <c r="M29" s="9"/>
@@ -2170,7 +2170,7 @@
       <c r="I41" s="7">
         <v>19000000</v>
       </c>
-      <c r="J41" s="30">
+      <c r="J41" s="29">
         <v>46218</v>
       </c>
       <c r="K41" s="7"/>

--- a/data/260815_자금관리_REV03.xlsx
+++ b/data/260815_자금관리_REV03.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CM\Desktop\테스트\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\테스트\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8B4C55-91B6-42AE-9663-538249F63A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -573,11 +573,11 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -881,13 +881,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
       <c r="G1" s="28"/>
       <c r="I1" s="3" t="s">
         <v>61</v>
@@ -906,11 +906,11 @@
       </c>
     </row>
     <row r="2" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="28"/>
       <c r="I2" s="26">
         <f>SUMIF(H4:H45,"계약금",G4:G45)</f>
@@ -1952,7 +1952,7 @@
         <f>G34*0.3</f>
         <v>171000000</v>
       </c>
-      <c r="J34" s="31">
+      <c r="J34" s="30">
         <v>46249</v>
       </c>
       <c r="K34" s="7"/>
